--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>MeleeDamage</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
   </si>
   <si>
     <t>SkillDamage</t>
@@ -185,20 +188,20 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,8 +426,8 @@
     <col customWidth="1" min="4" max="4" width="26.75"/>
     <col customWidth="1" min="5" max="5" width="23.25"/>
     <col customWidth="1" min="6" max="6" width="17.5"/>
-    <col customWidth="1" min="7" max="7" width="22.38"/>
-    <col customWidth="1" min="8" max="25" width="11.0"/>
+    <col customWidth="1" min="7" max="8" width="22.38"/>
+    <col customWidth="1" min="9" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -455,6 +458,7 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -475,10 +479,12 @@
       <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -496,71 +502,77 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D4" s="3">
         <v>0.0</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>90.0</v>
       </c>
       <c r="F4" s="3">
         <v>10.0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="H4" s="3">
         <v>10.0</v>
       </c>
-      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -578,16 +590,17 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>14</v>
+      <c r="A5" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>16</v>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -598,10 +611,12 @@
       <c r="F5" s="3">
         <v>20.0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="H5" s="3">
         <v>10.0</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -619,16 +634,17 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>17</v>
+      <c r="A6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="3">
         <v>2.0</v>
@@ -639,10 +655,12 @@
       <c r="F6" s="3">
         <v>30.0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="3">
         <v>10.0</v>
       </c>
-      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -660,30 +678,33 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8">
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3">
         <v>0.0</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="3">
         <v>90.0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="3">
         <v>10.0</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="H7" s="3">
         <v>10.0</v>
       </c>
-      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -701,30 +722,33 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8">
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3">
         <v>1.0</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="3">
         <v>80.0</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="3">
         <v>20.0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="3">
         <v>10.0</v>
       </c>
-      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -742,30 +766,33 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="8">
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3">
         <v>2.0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="3">
         <v>100.0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="3">
         <v>30.0</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="H9" s="3">
         <v>10.0</v>
       </c>
-      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -783,6 +810,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
@@ -810,6 +838,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -837,6 +866,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
@@ -864,6 +894,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -891,6 +922,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -918,6 +950,7 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
@@ -945,6 +978,7 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
@@ -972,6 +1006,7 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
@@ -999,6 +1034,7 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
@@ -1026,6 +1062,7 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
@@ -1053,6 +1090,7 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
@@ -1080,6 +1118,7 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
@@ -1107,6 +1146,7 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
@@ -1134,6 +1174,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
@@ -1161,6 +1202,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
@@ -1188,6 +1230,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
@@ -1215,6 +1258,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
@@ -1242,6 +1286,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
@@ -1269,6 +1314,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
@@ -1296,6 +1342,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
@@ -1323,6 +1370,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
@@ -1350,6 +1398,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
@@ -1377,6 +1426,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
@@ -1404,6 +1454,7 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
@@ -1431,6 +1482,7 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
@@ -1458,6 +1510,7 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
@@ -1485,6 +1538,7 @@
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
@@ -1512,6 +1566,7 @@
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
@@ -1539,6 +1594,7 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
@@ -1566,6 +1622,7 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
@@ -1593,6 +1650,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
@@ -1620,6 +1678,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
@@ -1647,6 +1706,7 @@
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
@@ -1674,6 +1734,7 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
@@ -1701,6 +1762,7 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
@@ -1728,6 +1790,7 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
@@ -1755,6 +1818,7 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
@@ -1782,6 +1846,7 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
@@ -1809,6 +1874,7 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
@@ -1836,6 +1902,7 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
@@ -1863,6 +1930,7 @@
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
@@ -1890,6 +1958,7 @@
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
@@ -1917,6 +1986,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
@@ -1944,6 +2014,7 @@
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
@@ -1971,6 +2042,7 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
@@ -1998,6 +2070,7 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
@@ -2025,6 +2098,7 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
@@ -2052,6 +2126,7 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
@@ -2079,6 +2154,7 @@
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
@@ -2106,6 +2182,7 @@
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
@@ -2133,6 +2210,7 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
@@ -2160,6 +2238,7 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
@@ -2187,6 +2266,7 @@
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
@@ -2214,6 +2294,7 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
@@ -2241,6 +2322,7 @@
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
@@ -2268,6 +2350,7 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
@@ -2295,6 +2378,7 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
@@ -2322,6 +2406,7 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
@@ -2349,6 +2434,7 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
@@ -2376,6 +2462,7 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
@@ -2403,6 +2490,7 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
@@ -2430,6 +2518,7 @@
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
@@ -2457,6 +2546,7 @@
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
@@ -2484,6 +2574,7 @@
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
@@ -2511,6 +2602,7 @@
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
@@ -2538,6 +2630,7 @@
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
@@ -2565,6 +2658,7 @@
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
@@ -2592,6 +2686,7 @@
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
@@ -2619,6 +2714,7 @@
       <c r="W77" s="3"/>
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
+      <c r="Z77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
@@ -2646,6 +2742,7 @@
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
+      <c r="Z78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
@@ -2673,6 +2770,7 @@
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
+      <c r="Z79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
@@ -2700,6 +2798,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
+      <c r="Z80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
@@ -2727,6 +2826,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
       <c r="Y81" s="3"/>
+      <c r="Z81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
@@ -2754,6 +2854,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
@@ -2781,6 +2882,7 @@
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
+      <c r="Z83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
@@ -2808,6 +2910,7 @@
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
+      <c r="Z84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
@@ -2835,6 +2938,7 @@
       <c r="W85" s="3"/>
       <c r="X85" s="3"/>
       <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
@@ -2862,6 +2966,7 @@
       <c r="W86" s="3"/>
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
@@ -2889,6 +2994,7 @@
       <c r="W87" s="3"/>
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
@@ -2916,6 +3022,7 @@
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
@@ -2943,6 +3050,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
+      <c r="Z89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
@@ -2970,6 +3078,7 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
@@ -2997,6 +3106,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
+      <c r="Z91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
@@ -3024,6 +3134,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
+      <c r="Z92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
@@ -3051,6 +3162,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
       <c r="Y93" s="3"/>
+      <c r="Z93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
@@ -3078,6 +3190,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
@@ -3105,6 +3218,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
@@ -3132,6 +3246,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
+      <c r="Z96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
@@ -3159,6 +3274,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
+      <c r="Z97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
@@ -3186,6 +3302,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
+      <c r="Z98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
@@ -3213,6 +3330,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
       <c r="Y99" s="3"/>
+      <c r="Z99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
@@ -3240,6 +3358,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
+      <c r="Z100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
@@ -3267,6 +3386,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
+      <c r="Z101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
@@ -3294,6 +3414,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
+      <c r="Z102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
@@ -3321,6 +3442,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
+      <c r="Z103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
@@ -3348,6 +3470,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
+      <c r="Z104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
@@ -3375,6 +3498,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
       <c r="Y105" s="3"/>
+      <c r="Z105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
@@ -3402,6 +3526,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
+      <c r="Z106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
@@ -3429,6 +3554,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
+      <c r="Z107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
@@ -3456,6 +3582,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
       <c r="Y108" s="3"/>
+      <c r="Z108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
@@ -3483,6 +3610,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
       <c r="Y109" s="3"/>
+      <c r="Z109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
@@ -3510,6 +3638,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
+      <c r="Z110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
@@ -3537,6 +3666,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
       <c r="Y111" s="3"/>
+      <c r="Z111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
@@ -3564,6 +3694,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
       <c r="Y112" s="3"/>
+      <c r="Z112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
@@ -3591,6 +3722,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
       <c r="Y113" s="3"/>
+      <c r="Z113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
@@ -3618,6 +3750,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
       <c r="Y114" s="3"/>
+      <c r="Z114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
@@ -3645,6 +3778,7 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
+      <c r="Z115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
@@ -3672,6 +3806,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
+      <c r="Z116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
@@ -3699,6 +3834,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
+      <c r="Z117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
@@ -3726,6 +3862,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
+      <c r="Z118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
@@ -3753,6 +3890,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
+      <c r="Z119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
@@ -3780,6 +3918,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
       <c r="Y120" s="3"/>
+      <c r="Z120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
@@ -3807,6 +3946,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
+      <c r="Z121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
@@ -3834,6 +3974,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
+      <c r="Z122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
@@ -3861,6 +4002,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
+      <c r="Z123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
@@ -3888,6 +4030,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
+      <c r="Z124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
@@ -3915,6 +4058,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
+      <c r="Z125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
@@ -3942,6 +4086,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
       <c r="Y126" s="3"/>
+      <c r="Z126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
@@ -3969,6 +4114,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
+      <c r="Z127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
@@ -3996,6 +4142,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
+      <c r="Z128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
@@ -4023,6 +4170,7 @@
       <c r="W129" s="3"/>
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
+      <c r="Z129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
@@ -4050,6 +4198,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
+      <c r="Z130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
@@ -4077,6 +4226,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
+      <c r="Z131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
@@ -4104,6 +4254,7 @@
       <c r="W132" s="3"/>
       <c r="X132" s="3"/>
       <c r="Y132" s="3"/>
+      <c r="Z132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
@@ -4131,6 +4282,7 @@
       <c r="W133" s="3"/>
       <c r="X133" s="3"/>
       <c r="Y133" s="3"/>
+      <c r="Z133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
@@ -4158,6 +4310,7 @@
       <c r="W134" s="3"/>
       <c r="X134" s="3"/>
       <c r="Y134" s="3"/>
+      <c r="Z134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
@@ -4185,6 +4338,7 @@
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
       <c r="Y135" s="3"/>
+      <c r="Z135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
@@ -4212,6 +4366,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
+      <c r="Z136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
@@ -4239,6 +4394,7 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
+      <c r="Z137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
@@ -4266,6 +4422,7 @@
       <c r="W138" s="3"/>
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
+      <c r="Z138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
@@ -4293,6 +4450,7 @@
       <c r="W139" s="3"/>
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
+      <c r="Z139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
@@ -4320,6 +4478,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
+      <c r="Z140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
@@ -4347,6 +4506,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
+      <c r="Z141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
@@ -4374,6 +4534,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
+      <c r="Z142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
@@ -4401,6 +4562,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
+      <c r="Z143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
@@ -4428,6 +4590,7 @@
       <c r="W144" s="3"/>
       <c r="X144" s="3"/>
       <c r="Y144" s="3"/>
+      <c r="Z144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
@@ -4455,6 +4618,7 @@
       <c r="W145" s="3"/>
       <c r="X145" s="3"/>
       <c r="Y145" s="3"/>
+      <c r="Z145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
@@ -4482,6 +4646,7 @@
       <c r="W146" s="3"/>
       <c r="X146" s="3"/>
       <c r="Y146" s="3"/>
+      <c r="Z146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
@@ -4509,6 +4674,7 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
+      <c r="Z147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
@@ -4536,6 +4702,7 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
+      <c r="Z148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
@@ -4563,6 +4730,7 @@
       <c r="W149" s="3"/>
       <c r="X149" s="3"/>
       <c r="Y149" s="3"/>
+      <c r="Z149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
@@ -4590,6 +4758,7 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
+      <c r="Z150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
@@ -4617,6 +4786,7 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
+      <c r="Z151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
@@ -4644,6 +4814,7 @@
       <c r="W152" s="3"/>
       <c r="X152" s="3"/>
       <c r="Y152" s="3"/>
+      <c r="Z152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
@@ -4671,6 +4842,7 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
+      <c r="Z153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
@@ -4698,6 +4870,7 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
+      <c r="Z154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
@@ -4725,6 +4898,7 @@
       <c r="W155" s="3"/>
       <c r="X155" s="3"/>
       <c r="Y155" s="3"/>
+      <c r="Z155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
@@ -4752,6 +4926,7 @@
       <c r="W156" s="3"/>
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
+      <c r="Z156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
@@ -4779,6 +4954,7 @@
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
+      <c r="Z157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
@@ -4806,6 +4982,7 @@
       <c r="W158" s="3"/>
       <c r="X158" s="3"/>
       <c r="Y158" s="3"/>
+      <c r="Z158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
@@ -4833,6 +5010,7 @@
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
+      <c r="Z159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
@@ -4860,6 +5038,7 @@
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="3"/>
+      <c r="Z160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
@@ -4887,6 +5066,7 @@
       <c r="W161" s="3"/>
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
+      <c r="Z161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
@@ -4914,6 +5094,7 @@
       <c r="W162" s="3"/>
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
+      <c r="Z162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
@@ -4941,6 +5122,7 @@
       <c r="W163" s="3"/>
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
+      <c r="Z163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
@@ -4968,6 +5150,7 @@
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
       <c r="Y164" s="3"/>
+      <c r="Z164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
@@ -4995,6 +5178,7 @@
       <c r="W165" s="3"/>
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
+      <c r="Z165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
@@ -5022,6 +5206,7 @@
       <c r="W166" s="3"/>
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
+      <c r="Z166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
@@ -5049,6 +5234,7 @@
       <c r="W167" s="3"/>
       <c r="X167" s="3"/>
       <c r="Y167" s="3"/>
+      <c r="Z167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
@@ -5076,6 +5262,7 @@
       <c r="W168" s="3"/>
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
+      <c r="Z168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
@@ -5103,6 +5290,7 @@
       <c r="W169" s="3"/>
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
+      <c r="Z169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
@@ -5130,6 +5318,7 @@
       <c r="W170" s="3"/>
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
+      <c r="Z170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
@@ -5157,6 +5346,7 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
+      <c r="Z171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
@@ -5184,6 +5374,7 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
+      <c r="Z172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
@@ -5211,6 +5402,7 @@
       <c r="W173" s="3"/>
       <c r="X173" s="3"/>
       <c r="Y173" s="3"/>
+      <c r="Z173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
@@ -5238,6 +5430,7 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
+      <c r="Z174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
@@ -5265,6 +5458,7 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
+      <c r="Z175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
@@ -5292,6 +5486,7 @@
       <c r="W176" s="3"/>
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
+      <c r="Z176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
@@ -5319,6 +5514,7 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
+      <c r="Z177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
@@ -5346,6 +5542,7 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
+      <c r="Z178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
@@ -5373,6 +5570,7 @@
       <c r="W179" s="3"/>
       <c r="X179" s="3"/>
       <c r="Y179" s="3"/>
+      <c r="Z179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
@@ -5400,6 +5598,7 @@
       <c r="W180" s="3"/>
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
+      <c r="Z180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
@@ -5427,6 +5626,7 @@
       <c r="W181" s="3"/>
       <c r="X181" s="3"/>
       <c r="Y181" s="3"/>
+      <c r="Z181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
@@ -5454,6 +5654,7 @@
       <c r="W182" s="3"/>
       <c r="X182" s="3"/>
       <c r="Y182" s="3"/>
+      <c r="Z182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
@@ -5481,6 +5682,7 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
+      <c r="Z183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
@@ -5508,6 +5710,7 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
+      <c r="Z184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
@@ -5535,6 +5738,7 @@
       <c r="W185" s="3"/>
       <c r="X185" s="3"/>
       <c r="Y185" s="3"/>
+      <c r="Z185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
@@ -5562,6 +5766,7 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
+      <c r="Z186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
@@ -5589,6 +5794,7 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
+      <c r="Z187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
@@ -5616,6 +5822,7 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
+      <c r="Z188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
@@ -5643,6 +5850,7 @@
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
       <c r="Y189" s="3"/>
+      <c r="Z189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
@@ -5670,6 +5878,7 @@
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
+      <c r="Z190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
@@ -5697,6 +5906,7 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
+      <c r="Z191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
@@ -5724,6 +5934,7 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
+      <c r="Z192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
@@ -5751,6 +5962,7 @@
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
       <c r="Y193" s="3"/>
+      <c r="Z193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
@@ -5778,6 +5990,7 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
+      <c r="Z194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
@@ -5805,6 +6018,7 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
+      <c r="Z195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
@@ -5832,6 +6046,7 @@
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
+      <c r="Z196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
@@ -5859,6 +6074,7 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
+      <c r="Z197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
@@ -5886,6 +6102,7 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
+      <c r="Z198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
@@ -5913,6 +6130,7 @@
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
       <c r="Y199" s="3"/>
+      <c r="Z199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
@@ -5940,6 +6158,7 @@
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="3"/>
+      <c r="Z200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
@@ -5967,6 +6186,7 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
+      <c r="Z201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
@@ -5994,6 +6214,7 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
+      <c r="Z202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
@@ -6021,6 +6242,7 @@
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
       <c r="Y203" s="3"/>
+      <c r="Z203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
@@ -6048,6 +6270,7 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
+      <c r="Z204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
@@ -6075,6 +6298,7 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
+      <c r="Z205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
@@ -6102,6 +6326,7 @@
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
+      <c r="Z206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
@@ -6129,6 +6354,7 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
+      <c r="Z207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
@@ -6156,6 +6382,7 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
+      <c r="Z208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
@@ -6183,6 +6410,7 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
+      <c r="Z209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
@@ -6210,6 +6438,7 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
+      <c r="Z210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
@@ -6237,6 +6466,7 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
+      <c r="Z211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
@@ -6264,6 +6494,7 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
+      <c r="Z212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
@@ -6291,6 +6522,7 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
+      <c r="Z213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
@@ -6318,6 +6550,7 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
+      <c r="Z214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
@@ -6345,6 +6578,7 @@
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
+      <c r="Z215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
@@ -6372,6 +6606,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
+      <c r="Z216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
@@ -6399,6 +6634,7 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
+      <c r="Z217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
@@ -6426,6 +6662,7 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
+      <c r="Z218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
@@ -6453,6 +6690,7 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
+      <c r="Z219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
@@ -6480,6 +6718,7 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
+      <c r="Z220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
